--- a/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:04</t>
+    <t xml:space="preserve">2026-09-09 22:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:56</t>
+    <t xml:space="preserve">2026-09-18 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:20</t>
+    <t xml:space="preserve">2026-09-23 12:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:23</t>
+    <t xml:space="preserve">2026-10-02 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:58</t>
+    <t xml:space="preserve">2026-10-04 08:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:42</t>
+    <t xml:space="preserve">2026-10-05 09:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
